--- a/Frontend/my-app/public/Pattern_Naming_Reference.xlsx
+++ b/Frontend/my-app/public/Pattern_Naming_Reference.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -779,7 +779,7 @@
       </c>
     </row>
     <row r="4" ht="57.95" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Size prefix words</t>
         </is>
@@ -796,7 +796,7 @@
       </c>
     </row>
     <row r="5" ht="57.95" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Size prefix words</t>
         </is>
@@ -813,204 +813,221 @@
       </c>
     </row>
     <row r="6" ht="57.95" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Size prefix words</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Women's sizes carry a W- prefix</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>W-XS · W-S · W-M · W-L · W-XL · W-2XL, and the youth-graded W-YXXS · W-YXS · W-YS · W-YM · W-YL · W-YXL. Name the pattern group with the code itself - "W-M Front", "W-YL Back". The order sheet may write it any way at all: the separator is ignored (W-M = W M = WM), and Women / Womens / Women's / Ladies are all read, with Adult or Youth optional on either side ("Women Adult Large", "Youth Women Small"). Full list on 'Size Prefixes'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="57.95" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Two pattern files</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Adult and youth are graded separately</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>A job attaches an Adult pattern .ai, a Youth pattern .ai, or both - neither is required on its own, and which ones are needed is worked out from the order's own sizes. The YOUTH file carries YXS-YXL, the toddler codes 1T-10T and the infant months 1M-12M; every other size is looked up in the ADULT file. If only one file is attached, every size falls back to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="57.95" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A job attaches an Adult pattern .ai, a Youth pattern .ai, or both - neither is required on its own, and which ones are needed is worked out from the order's own sizes. The YOUTH file carries YXS-YXL, the women's youth codes W-YXXS-W-YXL, the toddler codes 1T-10T and the infant months 1M-12M; every other size - including the women's adult codes W-XS to W-2XL - is looked up in the ADULT file. If only one file is attached, every size falls back to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="57.95" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Inside each piece</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>No 'base-path' needed here</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>'base-path' is a MOCKUP-side name and never exists in the pattern file. Here the script takes the LARGEST-AREA path in the group as the cut outline (findPlacementPath), so the outline needs no name at all. Just make sure the real outline is the biggest path in the group — a stray oversized guide rectangle would be picked instead.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="57.95" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9" ht="57.95" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Inside each piece</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Don't worry about stroke width</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>The script pins every pattern cut outline to 3pt itself (PATTERN_OUTLINE_PT = 3), right after the piece is duplicated and before anything is measured. Draw it at whatever width you like. The 3pt rule you DO have to follow manually is on the mockup's 'base-path'.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="57.95" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10" ht="57.95" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Inside each piece</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Size tag = text, not a name</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Each piece carries a small text frame with the size in it. The script rewrites it to the full part name ("XL" becomes "XL Short Sleeve Right") and grows the little background box behind it to fit. What matters is the TEXT content, not the object's name — accepted words are on the 'Size Tag Words' sheet.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="57.95" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="57.95" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Size tag rules</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Spelling is forgiving</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Spaces and hyphens are stripped before comparing, so "X-Large", "X-LARGE" and "xlarge" are all the same word.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="57.95" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="57.95" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Size tag rules</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Any size word is accepted, on any size</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>The global list matches any size word at all — a pattern tag that still says "X-Large" gets renamed correctly even on an "XL" order. This exists because pattern pieces often carry a stale sample size baked in from when they were drawn; an exact-match-only rule left that old text visible UNDER the new tag box, garbling the JPG.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="57.95" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13" ht="57.95" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Size tag rules</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Single letters are scoped</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>s / m / l are deliberately NOT in the global list — too easy to hit by accident on unrelated artwork. They are accepted only for the size currently being processed. This was added because Hood pieces carried a one-letter "s" tag, so Small hoods silently kept their pattern text while XL and 2XL hoods renamed fine.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="57.95" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14" ht="57.95" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sheets in this file</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Pattern Names</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Every group name, by section, with worked examples for Small and XL.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="57.95" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15" ht="57.95" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sheets in this file</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Size Prefixes</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Order-sheet size code → the word that must appear in the pattern group name.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="57.95" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16" ht="57.95" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Sheets in this file</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Size Tag Words</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Every spelling the size-tag TEXT may use and still be renamed correctly.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="57.95" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Sheets in this file</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Inside a Piece</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>What each pattern group must contain, and what the script does to it.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Companion file</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Mockup_Naming_Reference.xlsx</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Same folder. Covers the MOCKUP (test print) file — panel design groups, base-path, LOCAL-TAG, Center / Pattern / Match names and the per-feature checklist.</t>
         </is>
@@ -1028,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1590,11 +1607,85 @@
       </c>
     </row>
     <row r="22" ht="50.1" customHeight="1">
-      <c r="A22" s="26" t="n"/>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="29" t="n"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>5. Women's sizes</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>{Size} {Part}, with a W- code</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>W-M Front</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>W-2XL Front</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Nothing about the part name changes - only the size prefix. Every part on this sheet works the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>5. Women's sizes</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>{Size} Short Sleeve</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>W-M Short Sleeve</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>W-2XL Short Sleeve</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>W-M SS · Women M Short Sleeve · Women Medium SS - the size and the part are each matched on their own aliases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>5. Women's sizes</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>{Size} {Part}, youth-graded</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>W-YL Front</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>W-YXL Back</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Cut from the YOUTH pattern file, not the adult one. W-YXXS has no plain-youth counterpart.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:E21"/>
@@ -1612,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1652,14 +1743,14 @@
     <row r="2" ht="26.1" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>XS · XSmall  or  X-Small</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
           <t>XS</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
           <t>XS Front</t>
@@ -1672,7 +1763,7 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>Adult XS · AXS</t>
+          <t>Extra Small · Adult XS · AXS</t>
         </is>
       </c>
     </row>
@@ -1726,14 +1817,14 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>M · Adult Medium · Adult M · AM</t>
+          <t>M · Adult Medium · Adult Med · Adult M · AM</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26.1" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>L  or  Large</t>
+          <t>L · Lg  or  Large</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1753,21 +1844,21 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>L · Adult Large · Adult L · AL</t>
+          <t>L · Adult Large · Adult Lg · Adult L · AL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26.1" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>XL · XLarge  or  X-Large</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>XL Front</t>
@@ -1780,14 +1871,14 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Adult XL · AXL</t>
+          <t>Extra Large · Adult XL · AXL</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26.1" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>XXL  or  2XL</t>
+          <t>XXL · 2XL · XXLarge  or  2X-Large</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1807,14 +1898,14 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>XXL · Adult 2XL · Adult XXL · A2XL · AXXL</t>
+          <t>Adult 2XL · Adult XXL · A2XL · AXXL</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26.1" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>XXXL  or  3XL</t>
+          <t>XXXL · 3XL  or  XXXLarge</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1834,14 +1925,14 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>XXXL · Adult 3XL · Adult XXXL · A3XL · AXXXL</t>
+          <t>Adult 3XL · Adult XXXL · A3XL · AXXXL</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26.1" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>XXXXL  or  4XL</t>
+          <t>XXXXL · 4XL  or  4XLarge</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1861,7 +1952,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>XXXXL · Adult 4XL · Adult XXXXL · A4XL · AXXXXL</t>
+          <t>Adult 4XL · Adult XXXXL · A4XL · AXXXXL</t>
         </is>
       </c>
     </row>
@@ -1969,7 +2060,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Youth L</t>
+          <t>Youth L · Youth Lg</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2087,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Youth XL</t>
+          <t>Youth XL · Youth XLarge</t>
         </is>
       </c>
     </row>
@@ -2057,54 +2148,378 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>AXS / AS / AM / AL / AXL / A2XL ...</t>
+          <t>W-XS</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>the same as without the A</t>
+          <t>W-XS</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>AM  →  Medium Front</t>
+          <t>W-XS Front</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Adult, A-prefixed</t>
+          <t>Women's (adult file)</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>The A just pairs visually with the youth Y — it is never a distinct size.</t>
+          <t>W XS · WXS · Women XS · Womens XS · Women's XS · Ladies XS · Women Adult XS · Adult Women XS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>anything else (e.g. 5XL)</t>
+          <t>W-S</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
+          <t>W-S</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>W-S Front</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Women's (adult file)</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>W S · WS · Women S · Women Small · Womens Small · Ladies Small · W Small · Women Adult Small</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>W-M</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>W-M</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>W-M Front</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Women's (adult file)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>W M · WM · Women M · Women Medium · Women Med · Womens Medium · Ladies M · W Med · Women Adult Medium · Adult Women M</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>W-L</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>W-L</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>W-L Front</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Women's (adult file)</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>W L · WL · Women L · Women Large · Womens Large · Ladies Large · W Lg · Women Adult Large · Adult Women L</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>W-XL</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>W-XL</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>W-XL Front</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Women's (adult file)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>W XL · WXL · Women XL · Women X-Large · W XLarge · Ladies XL · Women Adult XL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>W-2XL</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>W-2XL</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>W-2XL Front</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Women's (adult file)</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>W 2XL · W2XL · WXXL · W-XXL · Women 2XL · Women XXL · Women XXLarge · Women Adult 2XL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>W-YXXS</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>W-YXXS</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>W-YXXS Front</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Women's (youth file)</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>WYXXS · Women YXXS · Womens YXXS · Women Youth XXS · Women Youth XXS · Youth Women XXS · W Youth XXS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>W-YXS</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>W-YXS</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>W-YXS Front</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Women's (youth file)</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>WYXS · Women YXS · Womens YXS · Women Youth XS · Women Youth XS · Youth Women XS · W Youth XS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>W-YS</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>W-YS</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>W-YS Front</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Women's (youth file)</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>WYS · Women YS · Womens YS · Women Youth S · Women Youth Small · Youth Women S · W Youth S</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>W-YM</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>W-YM</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>W-YM Front</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Women's (youth file)</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>WYM · Women YM · Womens YM · Women Youth M · Women Youth Medium · Youth Women M · W Youth M</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>W-YL</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>W-YL</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>W-YL Front</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Women's (youth file)</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>WYL · Women YL · Womens YL · Women Youth L · Women Youth Large · Youth Women L · W Youth L</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>W-YXL</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>W-YXL</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>W-YXL Front</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Women's (youth file)</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>WYXL · Women YXL · Womens YXL · Women Youth XL · Women Youth XL · Youth Women XL · W Youth XL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AXS / AS / AM / AL / AXL / A2XL ...</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>the same as without the A</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>AM  →  Medium Front</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Adult, A-prefixed</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>The A just pairs visually with the youth Y — it is never a distinct size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>anything else (e.g. 5XL · S/M)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
           <t>used exactly as written</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>5XL Front</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Pass-through</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Nothing extra is tried.</t>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Nothing extra is tried, so the pattern must carry that exact name. Combined sizes such as S/M are not a family the script knows.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2346,6 +2761,270 @@
       <c r="D10" s="4" t="inlineStr">
         <is>
           <t>In the global word list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>W-XS</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>wxs · xs · xsmall · extrasmall · womenxs · womensxs · ladiesxs</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>W-S</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ws · s · small · sm · womensmall · womenssmall · ladiessmall</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>W-M</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>wm · m · medium · med · womenm · womenmedium · womensm · womensmedium</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>W-L</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>wl · l · large · lg · womenl · womenlarge · womensl · womenslarge</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>W-XL</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>wxl · xl · xlarge · extralarge · womenxl · womensxl · ladiesxl</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>W-2XL</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>w2xl · 2xl · xxl · 2xlarge · xxlarge · women2xl · womenxxl · womens2xl · womensxxl</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>W-YXXS</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>wyxxs · yxxs · xxs · youthxxs · womenyxxs · womenyouthxxs</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>W-YXS</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>wyxs · yxs · youthxs · womenyxs · womenyouthxs</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>W-YS</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>wys · ys · youths · youthsmall · womenys · womenyouths</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>W-YM</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>wym · ym · youthm · youthmedium · womenym · womenyouthm</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>W-YL</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>wyl · yl · youthl · youthlarge · womenyl · womenyouthl</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>W-YXL</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>any size word from the rows above</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>wyxl · yxl · youthxl · womenyxl · womenyouthxl</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>The whole women's list is scoped to this size, so a piece tagged with the plain letter ('M') is renamed correctly on a W-M order.</t>
         </is>
       </c>
     </row>
